--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.853477771829022</v>
+        <v>1.601190137922216</v>
       </c>
       <c r="D2" t="n">
-        <v>10.21741612392158</v>
+        <v>1.660330120137257</v>
       </c>
       <c r="E2" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F2" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.73923752724591</v>
+        <v>1.907626098177461</v>
       </c>
       <c r="D3" t="n">
-        <v>11.37551276548636</v>
+        <v>1.848520824391534</v>
       </c>
       <c r="E3" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F3" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.0288980730278</v>
+        <v>5.204695936867017</v>
       </c>
       <c r="D4" t="n">
-        <v>31.5609305064008</v>
+        <v>5.128651207290131</v>
       </c>
       <c r="E4" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F4" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.26796521515277</v>
+        <v>4.918544347462326</v>
       </c>
       <c r="D5" t="n">
-        <v>29.58534432579116</v>
+        <v>4.807618452941064</v>
       </c>
       <c r="E5" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F5" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.54447529376127</v>
+        <v>5.613477235236207</v>
       </c>
       <c r="D6" t="n">
-        <v>33.90120482876385</v>
+        <v>5.508945784674125</v>
       </c>
       <c r="E6" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F6" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.5093219589657</v>
+        <v>4.957764818331926</v>
       </c>
       <c r="D7" t="n">
-        <v>30.15020815178501</v>
+        <v>4.899408824665064</v>
       </c>
       <c r="E7" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F7" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.96193273535254</v>
+        <v>4.706314069494788</v>
       </c>
       <c r="D8" t="n">
-        <v>29.46786317868012</v>
+        <v>4.78852776653552</v>
       </c>
       <c r="E8" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F8" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.38119131500019</v>
+        <v>2.336943588687531</v>
       </c>
       <c r="D9" t="n">
-        <v>14.85358474648637</v>
+        <v>2.413707521304036</v>
       </c>
       <c r="E9" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F9" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.71369800898866</v>
+        <v>2.878475926460657</v>
       </c>
       <c r="D10" t="n">
-        <v>17.85099436665907</v>
+        <v>2.900786584582099</v>
       </c>
       <c r="E10" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F10" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.66986457689889</v>
+        <v>3.521352993746069</v>
       </c>
       <c r="D11" t="n">
-        <v>22.31911609013898</v>
+        <v>3.626856364647584</v>
       </c>
       <c r="E11" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F11" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.57287517778752</v>
+        <v>5.455592216390473</v>
       </c>
       <c r="D12" t="n">
-        <v>34.19479086945852</v>
+        <v>5.55665351628701</v>
       </c>
       <c r="E12" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F12" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.88088678304251</v>
+        <v>3.880644102244407</v>
       </c>
       <c r="D13" t="n">
-        <v>24.08796485435688</v>
+        <v>3.914294288832993</v>
       </c>
       <c r="E13" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F13" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.71987685492717</v>
+        <v>4.991979988925665</v>
       </c>
       <c r="D14" t="n">
-        <v>31.33902397764904</v>
+        <v>5.092591396367969</v>
       </c>
       <c r="E14" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F14" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>34.07135488399346</v>
+        <v>5.536595168648939</v>
       </c>
       <c r="D15" t="n">
-        <v>34.48280370376082</v>
+        <v>5.603455601861134</v>
       </c>
       <c r="E15" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F15" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>25.55156523738165</v>
+        <v>4.152129351074518</v>
       </c>
       <c r="D16" t="n">
-        <v>25.75116628795338</v>
+        <v>4.184564521792424</v>
       </c>
       <c r="E16" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F16" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>13.08224137935156</v>
+        <v>2.125864224144629</v>
       </c>
       <c r="D17" t="n">
-        <v>12.97130460417418</v>
+        <v>2.107836998178305</v>
       </c>
       <c r="E17" t="n">
-        <v>8.385731074550074</v>
+        <v>1.362681299614387</v>
       </c>
       <c r="F17" t="n">
-        <v>8.34323604747695</v>
+        <v>1.355775857715005</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
